--- a/docs/downloads/04/tbl_cm_chars_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_cm_chars_marovoay_ampijoroa.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -569,12 +569,6 @@
           <t>Célibataire</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -635,7 +629,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D13">
@@ -773,14 +767,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D19">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="20">
@@ -796,14 +790,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>317</v>
       </c>
       <c r="E20">
-        <v>0.6</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
@@ -819,36 +813,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D21">
-        <v>317</v>
+        <v>49</v>
       </c>
       <c r="E21">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>49</v>
-      </c>
-      <c r="E22">
         <v>9.4</v>
       </c>
     </row>
